--- a/data/trans_dic/IP04F-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP04F-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -513,7 +514,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que posee otra vivienda que se pueda utilizar como residencia aunque no la utilice habitualmente</t>
+          <t>Población que posee otra vivienda que se pueda utilizar como residencia aunque no la utilice habitualmente (tasa de respuesta: 99,22%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -631,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,1; 9,12</t>
+          <t>3,08; 9,54</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,89; 10,82</t>
+          <t>4,11; 10,84</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,44; 10,15</t>
+          <t>3,48; 10,2</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,17; 10,92</t>
+          <t>3,1; 10,53</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,88; 8,73</t>
+          <t>3,94; 8,42</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,42; 9,29</t>
+          <t>4,28; 9,42</t>
         </is>
       </c>
     </row>
@@ -711,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,41; 13,89</t>
+          <t>7,24; 13,6</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,55; 14,83</t>
+          <t>7,71; 14,27</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,01; 10,52</t>
+          <t>5,05; 10,44</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,61; 9,8</t>
+          <t>4,75; 9,91</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,83; 11,04</t>
+          <t>6,63; 10,87</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,83; 11,06</t>
+          <t>6,7; 10,95</t>
         </is>
       </c>
     </row>
@@ -791,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,45; 16,99</t>
+          <t>8,24; 17,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,47; 9,62</t>
+          <t>3,45; 9,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,78; 16,42</t>
+          <t>8,35; 16,92</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,18; 11,9</t>
+          <t>5,18; 11,71</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,15; 15,52</t>
+          <t>9,31; 15,61</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,01; 9,59</t>
+          <t>5,05; 9,52</t>
         </is>
       </c>
     </row>
@@ -871,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,3; 17,95</t>
+          <t>9,16; 17,84</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,02; 15,93</t>
+          <t>7,88; 16,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,98; 15,91</t>
+          <t>7,71; 15,67</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,88; 14,98</t>
+          <t>6,84; 14,76</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,51; 15,08</t>
+          <t>9,48; 15,37</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,28; 14,14</t>
+          <t>8,33; 14,14</t>
         </is>
       </c>
     </row>
@@ -951,32 +952,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,67; 12,31</t>
+          <t>8,59; 12,48</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,45; 10,93</t>
+          <t>7,26; 10,75</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,4; 10,87</t>
+          <t>7,31; 10,67</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,4; 9,55</t>
+          <t>6,22; 9,48</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,43; 11,16</t>
+          <t>8,47; 11,04</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,19; 9,73</t>
+          <t>7,24; 9,55</t>
         </is>
       </c>
     </row>
@@ -1001,4 +1002,706 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Población que posee otra vivienda que se pueda utilizar como residencia aunque no la utilice habitualmente (tasa de respuesta: 99,22%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>8316</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>9102</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>8891</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>7421</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>17207</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>16524</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>4469; 13844</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>5385; 14212</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>5059; 14816</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>3853; 13074</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>11456; 24459</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>10916; 24052</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>23671</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>22272</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>19633</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>17770</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>43304</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>40042</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>16918; 31798</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>16056; 29713</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>13522; 27920</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>12196; 25441</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>33223; 54487</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>31133; 50924</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>18894</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>11357</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>18557</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>14605</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>37451</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>25962</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>12781; 26380</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>6479; 17366</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>13133; 26625</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>9585; 21677</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>29086; 48782</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>18827; 35497</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>22248</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>19564</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>20154</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>17821</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>42402</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>37385</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>15572; 30320</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>13614; 28147</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>13831; 28104</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>11773; 25413</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>33113; 53670</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>28717; 48771</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>73130</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>62296</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>67235</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>57617</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>140364</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>119913</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>60499; 87864</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>50824; 75219</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>54791; 79969</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>45900; 69992</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>123057; 160411</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>104068; 137380</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP04F-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP04F-Edad-trans_dic.xlsx
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,08; 9,54</t>
+          <t>3,12; 9,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,11; 10,84</t>
+          <t>3,9; 11,33</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,48; 10,2</t>
+          <t>3,54; 10,35</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,1; 10,53</t>
+          <t>3,14; 10,01</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,94; 8,42</t>
+          <t>3,98; 8,19</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,28; 9,42</t>
+          <t>4,45; 9,34</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,24; 13,6</t>
+          <t>7,5; 13,57</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,71; 14,27</t>
+          <t>7,52; 14,54</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,05; 10,44</t>
+          <t>4,67; 10,48</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,75; 9,91</t>
+          <t>4,67; 10,06</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,63; 10,87</t>
+          <t>6,82; 11,21</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,7; 10,95</t>
+          <t>6,76; 10,89</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,24; 17,0</t>
+          <t>8,16; 16,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,45; 9,25</t>
+          <t>3,6; 9,43</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,35; 16,92</t>
+          <t>8,12; 17,1</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,18; 11,71</t>
+          <t>5,01; 11,59</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,31; 15,61</t>
+          <t>9,23; 15,42</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,05; 9,52</t>
+          <t>5,08; 9,29</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,16; 17,84</t>
+          <t>9,11; 17,98</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,88; 16,29</t>
+          <t>7,86; 15,89</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,71; 15,67</t>
+          <t>7,86; 15,48</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,84; 14,76</t>
+          <t>6,76; 15,03</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,48; 15,37</t>
+          <t>9,5; 15,52</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,33; 14,14</t>
+          <t>8,25; 13,94</t>
         </is>
       </c>
     </row>
@@ -952,32 +952,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,59; 12,48</t>
+          <t>8,75; 12,43</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,26; 10,75</t>
+          <t>7,2; 10,43</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,31; 10,67</t>
+          <t>7,37; 10,79</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,22; 9,48</t>
+          <t>6,36; 9,42</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,47; 11,04</t>
+          <t>8,49; 11,05</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,24; 9,55</t>
+          <t>7,27; 9,75</t>
         </is>
       </c>
     </row>
@@ -1182,32 +1182,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4469; 13844</t>
+          <t>4529; 13350</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5385; 14212</t>
+          <t>5108; 14853</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5059; 14816</t>
+          <t>5138; 15038</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3853; 13074</t>
+          <t>3903; 12435</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>11456; 24459</t>
+          <t>11568; 23784</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10916; 24052</t>
+          <t>11351; 23833</t>
         </is>
       </c>
     </row>
@@ -1300,32 +1300,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16918; 31798</t>
+          <t>17536; 31718</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16056; 29713</t>
+          <t>15668; 30283</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13522; 27920</t>
+          <t>12497; 28038</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12196; 25441</t>
+          <t>11982; 25811</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>33223; 54487</t>
+          <t>34178; 56198</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>31133; 50924</t>
+          <t>31420; 50627</t>
         </is>
       </c>
     </row>
@@ -1418,32 +1418,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>12781; 26380</t>
+          <t>12657; 25669</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6479; 17366</t>
+          <t>6760; 17706</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13133; 26625</t>
+          <t>12772; 26903</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9585; 21677</t>
+          <t>9274; 21467</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>29086; 48782</t>
+          <t>28837; 48177</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18827; 35497</t>
+          <t>18961; 34637</t>
         </is>
       </c>
     </row>
@@ -1536,32 +1536,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>15572; 30320</t>
+          <t>15483; 30567</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>13614; 28147</t>
+          <t>13572; 27460</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13831; 28104</t>
+          <t>14089; 27757</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11773; 25413</t>
+          <t>11633; 25874</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>33113; 53670</t>
+          <t>33166; 54209</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>28717; 48771</t>
+          <t>28468; 48072</t>
         </is>
       </c>
     </row>
@@ -1654,32 +1654,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>60499; 87864</t>
+          <t>61583; 87539</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>50824; 75219</t>
+          <t>50423; 73028</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>54791; 79969</t>
+          <t>55270; 80863</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>45900; 69992</t>
+          <t>46929; 69529</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>123057; 160411</t>
+          <t>123474; 160610</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>104068; 137380</t>
+          <t>104562; 140196</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP04F-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP04F-Edad-trans_dic.xlsx
@@ -520,13 +520,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -594,22 +594,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6,12%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5,98%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>5,73%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>6,94%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>6,12%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5,98%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,12; 9,2</t>
+          <t>3,44; 10,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,9; 11,33</t>
+          <t>3,17; 10,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,54; 10,35</t>
+          <t>3,1; 9,12</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,14; 10,01</t>
+          <t>3,89; 10,82</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,98; 8,19</t>
+          <t>3,88; 8,73</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,45; 9,34</t>
+          <t>4,42; 9,29</t>
         </is>
       </c>
     </row>
@@ -674,22 +674,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>7,34%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>6,92%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>10,12%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>10,69%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>7,34%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>6,92%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,5; 13,57</t>
+          <t>5,01; 10,52</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,52; 14,54</t>
+          <t>4,61; 9,8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,67; 10,48</t>
+          <t>7,41; 13,89</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,67; 10,06</t>
+          <t>7,55; 14,83</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,82; 11,21</t>
+          <t>6,83; 11,04</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,76; 10,89</t>
+          <t>6,83; 11,06</t>
         </is>
       </c>
     </row>
@@ -754,22 +754,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>11,79%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>7,89%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>12,18%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>6,05%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>11,79%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>7,89%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,16; 16,54</t>
+          <t>7,78; 16,42</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,6; 9,43</t>
+          <t>5,18; 11,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,12; 17,1</t>
+          <t>8,45; 16,99</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,01; 11,59</t>
+          <t>3,47; 9,62</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,23; 15,42</t>
+          <t>9,15; 15,52</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,08; 9,29</t>
+          <t>5,01; 9,59</t>
         </is>
       </c>
     </row>
@@ -834,22 +834,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>11,24%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>10,35%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>13,09%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>11,32%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>11,24%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>10,35%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,11; 17,98</t>
+          <t>7,98; 15,91</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,86; 15,89</t>
+          <t>6,88; 14,98</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,86; 15,48</t>
+          <t>9,3; 17,95</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,76; 15,03</t>
+          <t>8,02; 15,93</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,5; 15,52</t>
+          <t>9,51; 15,08</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,25; 13,94</t>
+          <t>8,28; 14,14</t>
         </is>
       </c>
     </row>
@@ -914,22 +914,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>8,97%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>7,81%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>10,39%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>8,9%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>8,97%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>7,81%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -952,32 +952,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,75; 12,43</t>
+          <t>7,4; 10,87</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,2; 10,43</t>
+          <t>6,4; 9,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,37; 10,79</t>
+          <t>8,67; 12,31</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,36; 9,42</t>
+          <t>7,45; 10,93</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,49; 11,05</t>
+          <t>8,43; 11,16</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,27; 9,75</t>
+          <t>7,19; 9,73</t>
         </is>
       </c>
     </row>
@@ -1032,13 +1032,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -1111,17 +1111,17 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>15</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1144,22 +1144,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>8891</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>7421</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
           <t>8316</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>9102</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>8891</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>7421</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1182,32 +1182,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4529; 13350</t>
+          <t>5005; 14753</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5108; 14853</t>
+          <t>3940; 13561</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5138; 15038</t>
+          <t>4498; 13227</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3903; 12435</t>
+          <t>5094; 14189</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>11568; 23784</t>
+          <t>11255; 25359</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11351; 23833</t>
+          <t>11277; 23713</t>
         </is>
       </c>
     </row>
@@ -1224,22 +1224,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>35</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>19633</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>17770</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>23671</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>22272</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>19633</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>17770</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1300,32 +1300,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17536; 31718</t>
+          <t>13411; 28143</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15668; 30283</t>
+          <t>11843; 25155</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12497; 28038</t>
+          <t>17334; 32468</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11982; 25811</t>
+          <t>15727; 30880</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>34178; 56198</t>
+          <t>34247; 55356</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>31420; 50627</t>
+          <t>31773; 51410</t>
         </is>
       </c>
     </row>
@@ -1342,22 +1342,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>16</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1380,22 +1380,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>18557</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>14605</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
           <t>18894</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>11357</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>18557</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>14605</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1418,32 +1418,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>12657; 25669</t>
+          <t>12239; 25847</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6760; 17706</t>
+          <t>9587; 22027</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12772; 26903</t>
+          <t>13115; 26360</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9274; 21467</t>
+          <t>6517; 18070</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>28837; 48177</t>
+          <t>28598; 48492</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18961; 34637</t>
+          <t>18698; 35749</t>
         </is>
       </c>
     </row>
@@ -1460,22 +1460,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>28</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1498,22 +1498,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>20154</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>17821</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>22248</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>19564</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>20154</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>17821</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1536,32 +1536,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>15483; 30567</t>
+          <t>14318; 28522</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>13572; 27460</t>
+          <t>11850; 25778</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14089; 27757</t>
+          <t>15806; 30506</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11633; 25874</t>
+          <t>13850; 27528</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>33166; 54209</t>
+          <t>33210; 52681</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>28468; 48072</t>
+          <t>28557; 48787</t>
         </is>
       </c>
     </row>
@@ -1578,22 +1578,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>105</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>94</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1616,22 +1616,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>67235</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>57617</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
           <t>73130</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>62296</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>67235</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>57617</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1654,32 +1654,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>61583; 87539</t>
+          <t>55435; 81500</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>50423; 73028</t>
+          <t>47226; 70514</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>55270; 80863</t>
+          <t>61013; 86633</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>46929; 69529</t>
+          <t>52170; 76515</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>123474; 160610</t>
+          <t>122576; 162201</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>104562; 140196</t>
+          <t>103401; 139952</t>
         </is>
       </c>
     </row>
